--- a/public/templates/process-docs/电缆沟开挖及回填工程质量隐蔽验收记录.xlsx
+++ b/public/templates/process-docs/电缆沟开挖及回填工程质量隐蔽验收记录.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">隐蔽工程项目</t>
@@ -138,25 +138,25 @@
     <t xml:space="preserve">项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">专业工长</t>
   </si>
   <si>
-    <t xml:space="preserve">刘彦堂</t>
+    <t xml:space="preserve">{{施工单位项目技术负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工标准
@@ -391,19 +391,19 @@
     <t xml:space="preserve">编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-0011-015-107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5028G01-0011-015-108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5028G01-0011-015-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5028G01-0011-015-110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5028G01-0011-015-111</t>
+    <t xml:space="preserve">{{工程编号}}-015-107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{工程编号}}-015-108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{工程编号}}-015-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{工程编号}}-015-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{工程编号}}-015-111</t>
   </si>
   <si>
     <t xml:space="preserve">施工单位
